--- a/flask_project/法規(缺失違反法規).xlsx
+++ b/flask_project/法規(缺失違反法規).xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Park_Chou\Desktop\flask_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA558A22-0D93-4927-BAA4-5CBEFE5D35A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3EFEDA-0042-4615-A743-A111FBD8B992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="0" windowWidth="15600" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7425" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="電氣" sheetId="1" r:id="rId1"/>
     <sheet name="排水" sheetId="4" r:id="rId2"/>
-    <sheet name="給水" sheetId="3" r:id="rId3"/>
-    <sheet name="電梯" sheetId="5" r:id="rId4"/>
-    <sheet name="高層建築" sheetId="7" r:id="rId5"/>
-    <sheet name="弱電 " sheetId="10" r:id="rId6"/>
-    <sheet name="發電機" sheetId="11" r:id="rId7"/>
-    <sheet name="太陽能" sheetId="12" r:id="rId8"/>
+    <sheet name="文件清冊" sheetId="13" r:id="rId3"/>
+    <sheet name="給水" sheetId="3" r:id="rId4"/>
+    <sheet name="電梯" sheetId="5" r:id="rId5"/>
+    <sheet name="高層建築" sheetId="7" r:id="rId6"/>
+    <sheet name="弱電 " sheetId="10" r:id="rId7"/>
+    <sheet name="發電機" sheetId="11" r:id="rId8"/>
+    <sheet name="太陽能" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -222,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="247">
   <si>
     <t>項次</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -731,10 +732,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.貫穿防火區劃牆壁或樓地板之風管，應在貫穿部位任一側之風管內裝設防火閘門或閘板，其與貫穿部位合成之構造，並應具有一小時以上之防火時效。                                                        2.貫穿防火區劃牆壁或樓地板之電力管線、通訊管線及給排水管線或管線匣，與貫穿部位合成之構造，應具有一小時以上之防火時效。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>用戶用電設備裝置規則表第27條</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -754,35 +751,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>七、升降機、電動起重機或類似可移動式機器裝設滑接導線供電者，除採用三百伏特以下絕緣導
-線或由一次側電壓三百伏特以下絕緣變壓器供電，或其接地電阻十歐姆（Ω）以下者外，導
-線與大地之絕緣電阻應保持表一○規定電阻值以上。新設時之絕緣電阻應在一百萬歐姆
-（MΩ）以上。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排水管之方向變換，基於彎曲管處之容許排水量、管內固體物流送、及
-清掃工具之插入等，應使用適當之異形管件組合施工，或使用二個45°接
-頭組成一個90°長彎曲管，使用規格外之特殊接頭，須經中央主管建築機
-關認可。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>給排水設備規範4.2.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通氣管之末端設計應符合下列規定：
-(1) 貫穿屋頂之通氣管，應伸出屋面15公分以上，向大氣開放。
-(2) 屋頂供遊憩或作為庭園、運動場、曬物場等用途時，主通氣管伸出屋面高度
-不得小於1.5公尺。管之末端兼作其他用途時，不得妨礙原通氣功能。
-(3) 通氣管末端接近本建築物或鄰接建築物之出入口、窗、換氣口等位置時，通
-氣管末端向大氣開放之開口部位置，應較該換氣用開口部之上端高60公分以
-上，或應距各換氣用開口部分水平距離3公尺以上。
-(4) 貫穿外壁之通氣管末端，應為不阻礙通氣管機能之構造。
-(5) 通氣管末端之開口部，不得位於建築物凸出部位之下部。
-(6) 通氣口有凍結而閉塞之顧慮者，通氣口之內徑應在75公釐以上；此通氣口徑
-增大時，應與建物內部或屋頂、外壁之內面相離300公釐以上。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1122,24 +1091,269 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>用戶用電設備裝置規則第884條</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管路轉折處未使用正確接頭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1 建築物或PV系統支撐架應採用第二章第五節規定之接地電極系統。PV組列設備接地導線應依第一百零三條規定連接至接地電極系統，該連接應為第八百八十二條第三款規定以外之額外連接。PV組列設備接地導線線徑應依前條規定選用。                                                                                                         
-                                                                                       2  第八百八十條第一項規定之PV 系統接地架構，應符合下列規定之一：
+2  第八百八十條第一項規定之PV 系統接地架構，應符合下列規定之一：
 一、非直接接地PV 系統輸出端之設備接地導線，若連接至接地電極系統相連之配電箱者，得作為
 該系統對地之唯一連接。
 二、直接接地PV 系統應以十四平方毫米以上之接地電極導線，連接至接地電極系統。
-                                                                                       3   PV 系統之接地電極不得與輸配電業或用戶配線系統接地搭接。該接地電極得直接連接至PV模組框架或支撐結構。接地電極導線線徑應依表九三～一規定選用，其接地電阻適用表九二規定。地面型PV 組列之支撐結構符合第九十八條規定者，得作為接地電極。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用戶用電設備裝置規則第884條</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>管路轉折處未使用正確接頭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.貫穿防火區劃牆壁或樓地板之風管，應在貫穿部位任一側之風管內裝設防火閘門或閘板，其與貫穿部位合成之構造，並應具有一小時以上之防火時效。                                            2.貫穿防火區劃牆壁或樓地板之電力管線、通訊管線及給排水管線或管線匣，與貫穿部位合成之構造，應具有一小時以上之防火時效。</t>
+3   PV 系統之接地電極不得與輸配電業或用戶配線系統接地搭接。該接地電極得直接連接至PV模組框架或支撐結構。接地電極導線線徑應依表九三～一規定選用，其接地電阻適用表九二規定。地面型PV 組列之支撐結構符合第九十八條規定者，得作為接地電極。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.貫穿防火區劃牆壁或樓地板之風管，應在貫穿部位任一側之風管內裝設防火閘門或閘板，其與貫穿部位合成之構造，並應具有一小時以上之防火時效。                                                                                                                                                                                                                                  2.貫穿防火區劃牆壁或樓地板之電力管線、通訊管線及給排水管線或管線匣，與貫穿部位合成之構造，應具有一小時以上之防火時效。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排水管之方向變換，基於彎曲管處之容許排水量、管內固體物流送、及清掃工具之插入等，應使用適當之異形管件組合施工，或使用二個45°接頭組成一個90°長彎曲管，使用規格外之特殊接頭，須經中央主管建築機關認可。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通氣管之末端設計應符合下列規定：
+(1) 貫穿屋頂之通氣管，應伸出屋面15公分以上，向大氣開放。
+(2) 屋頂供遊憩或作為庭園、運動場、曬物場等用途時，主通氣管伸出屋面高度不得小於1.5公尺。管之末端兼作其他用途時，不得妨礙原通氣功能。
+(3) 通氣管末端接近本建築物或鄰接建築物之出入口、窗、換氣口等位置時，通氣管末端向大氣開放之開口部位置，應較該換氣用開口部之上端高60公分以上，或距各換氣用開口部分水平距離3公尺以上。
+(4) 貫穿外壁之通氣管末端，應為不阻礙通氣管機能之構造。
+(5) 通氣管末端之開口部，不得位於建築物凸出部位之下部。
+(6) 通氣口有凍結而閉塞之顧慮者，通氣口之內徑應在75公釐以上；此通氣口徑增大時，應與建物內部或屋頂、外壁之內面相離300公釐以上。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未使用不燃材料</t>
+  </si>
+  <si>
+    <t>1.貫穿防火區劃牆壁或樓地板之風管，應在貫穿部位任一側之風管內裝設防火閘門或閘板，其與貫穿部位合成之構造，並應具有一小時以上之防火時效。
+2.貫穿防火區劃牆壁或樓地板之電力管線、通訊管線及給排水管線或管線匣，與貫穿部位合成之構造，應具有一小時以上之防火時效。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分項</t>
+  </si>
+  <si>
+    <t>問題</t>
+  </si>
+  <si>
+    <t>範例</t>
+  </si>
+  <si>
+    <t>文件清冊</t>
+  </si>
+  <si>
+    <t>設備點交清冊</t>
+  </si>
+  <si>
+    <t>使照影本</t>
+  </si>
+  <si>
+    <t>廠商資料表</t>
+  </si>
+  <si>
+    <t>建築現況竣工圖</t>
+  </si>
+  <si>
+    <t>營建</t>
+  </si>
+  <si>
+    <t>營建使照核准圖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">建築物專有、約定專用、共用、約定共用部分標示圖 </t>
+  </si>
+  <si>
+    <t>供公眾使用之開放空間之標示圖</t>
+  </si>
+  <si>
+    <t>景觀植栽圖</t>
+  </si>
+  <si>
+    <t>電氣現況竣工圖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">景觀、外牆及公設二工區照明設備現況竣工圖 </t>
+  </si>
+  <si>
+    <t>消防現況竣工圖</t>
+  </si>
+  <si>
+    <t>空調現況竣工圖</t>
+  </si>
+  <si>
+    <t>通風現況竣工圖</t>
+  </si>
+  <si>
+    <t>弱電現況竣工圖(電信,共同天線,網路,接地)</t>
+  </si>
+  <si>
+    <t>監控現況竣工圖(CCTV,中央監控,門禁,對講機,車道管制)</t>
+  </si>
+  <si>
+    <t>行動電話改善設備現況竣工圖</t>
+  </si>
+  <si>
+    <t>給水現況竣工圖</t>
+  </si>
+  <si>
+    <t>排水現況竣工圖(污水、廢水)</t>
+  </si>
+  <si>
+    <t>污水處理設備現況竣工圖</t>
+  </si>
+  <si>
+    <t>噴灌設備現況竣工圖</t>
+  </si>
+  <si>
+    <t>水景設備現況竣工圖</t>
+  </si>
+  <si>
+    <t>泳池或SPA或溫泉設備現況竣工圖</t>
+  </si>
+  <si>
+    <t>公共區裝修材料防火證明(認可通知書)</t>
+  </si>
+  <si>
+    <t>防火門防火證明(認可通知書)</t>
+  </si>
+  <si>
+    <t>低壓配電盤</t>
+  </si>
+  <si>
+    <t>發電機組</t>
+  </si>
+  <si>
+    <t>景觀照明設備</t>
+  </si>
+  <si>
+    <t>消防、撒水、泡沫機組</t>
+  </si>
+  <si>
+    <t>消防設備(火警、廣播、避難、滅火、排煙…等)</t>
+  </si>
+  <si>
+    <t>空調出廠證明</t>
+  </si>
+  <si>
+    <t>空調操作手冊</t>
+  </si>
+  <si>
+    <t>進排風設備(含地下室、發電機及梯廳間排煙設備)</t>
+  </si>
+  <si>
+    <t>監視、中央監控、門禁對講、停車管理、車道管制</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 共同天線(數位天線)  </t>
+  </si>
+  <si>
+    <t>行動電話改善設備</t>
+  </si>
+  <si>
+    <t>避雷針</t>
+  </si>
+  <si>
+    <t>揚水泵浦</t>
+  </si>
+  <si>
+    <t>污/廢水泵浦</t>
+  </si>
+  <si>
+    <t>水景設備</t>
+  </si>
+  <si>
+    <t>噴灌系統</t>
+  </si>
+  <si>
+    <t>雨水處理過濾設備</t>
+  </si>
+  <si>
+    <t>污水處理設備</t>
+  </si>
+  <si>
+    <t>泳池或SPA或溫泉設備</t>
+  </si>
+  <si>
+    <t>自來水過濾/活水</t>
+  </si>
+  <si>
+    <t>電梯/電扶梯(使用許可證)</t>
+  </si>
+  <si>
+    <t>機械停車/汽機車升降設備(使用許可證)</t>
+  </si>
+  <si>
+    <t>垃圾處理設備出廠及操作手冊</t>
+  </si>
+  <si>
+    <t>健身器材操作手冊</t>
+  </si>
+  <si>
+    <t>音響設備操作手冊</t>
+  </si>
+  <si>
+    <t>太陽能出廠證明</t>
+  </si>
+  <si>
+    <t>污水處理設備出廠及操作竣工圖</t>
+  </si>
+  <si>
+    <t>雨水回收設備出廠及操作手冊</t>
+  </si>
+  <si>
+    <t>機電</t>
+  </si>
+  <si>
+    <t>電梯車廂上方護欄高度</t>
+  </si>
+  <si>
+    <t>配電盤過門接地線法規</t>
+  </si>
+  <si>
+    <t>電信機房不得其他管路經過</t>
+  </si>
+  <si>
+    <t>防火管理人講習訓練教材</t>
+  </si>
+  <si>
+    <t>公寓大廈點交手冊</t>
+  </si>
+  <si>
+    <t>公設檢驗客戶問答</t>
+  </si>
+  <si>
+    <t>N、G相銅排接地線未銜接</t>
+  </si>
+  <si>
+    <t>過門接地線未施作</t>
+  </si>
+  <si>
+    <t>花線不得裝設之情形</t>
+  </si>
+  <si>
+    <t>避雷針電阻值高於規範值</t>
+  </si>
+  <si>
+    <t>太陽能隔離設備 載流直流導線未依規定裝設</t>
+  </si>
+  <si>
+    <t>太陽光電電源電路接地線徑小於14mm未有保護</t>
+  </si>
+  <si>
+    <t>太陽光電電源接地線徑小於2.0mm</t>
+  </si>
+  <si>
+    <t>太陽能警語標示</t>
+  </si>
+  <si>
+    <t>汙水處理設備泵浦絕緣阻值不足</t>
+  </si>
+  <si>
+    <t>電梯110%荷重報告書</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1147,7 +1361,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1197,8 +1411,32 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1221,6 +1459,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
       </patternFill>
     </fill>
   </fills>
@@ -1450,7 +1694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1512,35 +1756,98 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1554,54 +1861,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2212,7 +2476,7 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.85546875" customWidth="1"/>
+    <col min="3" max="3" width="126" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2227,19 +2491,19 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="330.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54"/>
-      <c r="B3" s="52"/>
+    <row r="3" spans="1:4" ht="285.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="37"/>
+      <c r="B3" s="43"/>
       <c r="C3" s="8" t="s">
         <v>85</v>
       </c>
@@ -2248,10 +2512,10 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53">
+      <c r="A4" s="36">
         <v>2</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="42" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -2259,8 +2523,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="230.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54"/>
-      <c r="B5" s="52"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="43"/>
       <c r="C5" s="14" t="s">
         <v>87</v>
       </c>
@@ -2269,28 +2533,28 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="53">
+      <c r="A6" s="36">
         <v>3</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="42" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="54"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="8" t="s">
+    <row r="7" spans="1:4" ht="345.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="37"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="28" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53">
+      <c r="A8" s="36">
         <v>4</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="38" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -2298,71 +2562,71 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="54"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="56">
+      <c r="A10" s="40">
         <v>5</v>
       </c>
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="41" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="195" x14ac:dyDescent="0.25">
-      <c r="A11" s="41"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="16" t="s">
+    <row r="11" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A11" s="31"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="26" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44">
+      <c r="A12" s="30">
         <v>6</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="32" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="41"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="16" t="s">
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="31"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="26" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44">
+      <c r="A14" s="30">
         <v>7</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="34" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A15" s="41"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="16" t="s">
+    <row r="15" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A15" s="31"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="26" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="44">
+      <c r="A16" s="30">
         <v>8</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="32" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -2370,17 +2634,17 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="41"/>
-      <c r="B17" s="42"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="44">
+      <c r="A18" s="30">
         <v>9</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -2388,17 +2652,17 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="41"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="44">
+      <c r="A20" s="30">
         <v>10</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="32" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2406,35 +2670,35 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="41"/>
-      <c r="B21" s="42"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="33"/>
       <c r="C21" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="44">
+      <c r="A22" s="30">
         <v>11</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="34" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A23" s="41"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="16" t="s">
+    <row r="23" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="31"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="26" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="44">
+      <c r="A24" s="30">
         <v>12</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="34" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2442,18 +2706,18 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="190.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="41"/>
-      <c r="B25" s="33"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="18"/>
-      <c r="D25" s="50" t="e" vm="3">
+      <c r="D25" s="27" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="44">
+      <c r="A26" s="30">
         <v>13</v>
       </c>
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="34" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -2461,8 +2725,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="276.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="41"/>
-      <c r="B27" s="33"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="19" t="s">
         <v>102</v>
       </c>
@@ -2471,10 +2735,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="44">
+      <c r="A28" s="30">
         <v>14</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="34" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2482,26 +2746,26 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="41"/>
-      <c r="B29" s="33"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="44">
+      <c r="A30" s="30">
         <v>15</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="45" t="s">
         <v>46</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="41"/>
-      <c r="B31" s="48"/>
+    <row r="31" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="31"/>
+      <c r="B31" s="39"/>
       <c r="C31" s="25" t="s">
         <v>74</v>
       </c>
@@ -2510,10 +2774,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="34">
+      <c r="A32" s="47">
         <v>16</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="42" t="s">
         <v>82</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2521,68 +2785,46 @@
       </c>
     </row>
     <row r="33" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
-      <c r="B33" s="32"/>
+      <c r="A33" s="44"/>
+      <c r="B33" s="46"/>
       <c r="C33" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="44"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="44"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="44">
+        <v>17</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="29"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A35" s="29"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="29">
-        <v>17</v>
-      </c>
-      <c r="B36" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="3" t="s">
+    <row r="37" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+      <c r="A37" s="44"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="26" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="240" x14ac:dyDescent="0.25">
-      <c r="A37" s="29"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="16" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A30:A31"/>
@@ -2595,6 +2837,28 @@
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A32:A35"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2608,7 +2872,7 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.42578125" customWidth="1"/>
+    <col min="3" max="3" width="161.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2623,64 +2887,64 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="30">
+      <c r="A2" s="51">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>171</v>
+      <c r="B2" s="52" t="s">
+        <v>166</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="28"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
       <c r="C3" s="13" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
+      <c r="A4" s="51">
         <v>2</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="52" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30"/>
-      <c r="B5" s="28"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="3" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30">
+      <c r="A6" s="51">
         <v>3</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="53" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30"/>
-      <c r="B7" s="36"/>
+    <row r="7" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="51"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30">
+      <c r="A8" s="51">
         <v>4</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="42" t="s">
         <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2688,102 +2952,111 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="27" t="s">
+      <c r="A9" s="51"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="48" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
+      <c r="A10" s="51">
         <v>5</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="19" t="s">
-        <v>120</v>
-      </c>
+      <c r="B10" s="46"/>
+      <c r="C10" s="49"/>
     </row>
     <row r="11" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="9" t="s">
-        <v>119</v>
-      </c>
+      <c r="A11" s="51"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="50"/>
     </row>
     <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30">
+      <c r="A12" s="51">
         <v>6</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="29" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
+      <c r="A14" s="51">
         <v>7</v>
       </c>
-      <c r="B14" s="30"/>
+      <c r="B14" s="51"/>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30">
+      <c r="A16" s="51">
         <v>8</v>
       </c>
-      <c r="B16" s="30"/>
+      <c r="B16" s="51"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30">
+      <c r="A18" s="51">
         <v>9</v>
       </c>
-      <c r="B18" s="30"/>
+      <c r="B18" s="51"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+      <c r="A20" s="51">
         <v>10</v>
       </c>
-      <c r="B20" s="30"/>
+      <c r="B20" s="51"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="51"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
+      <c r="A22" s="51">
         <v>11</v>
       </c>
-      <c r="B22" s="30"/>
+      <c r="B22" s="51"/>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="51"/>
       <c r="C23" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C9:C11"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A22:A23"/>
@@ -2799,12 +3072,6 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2813,6 +3080,685 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81AB99C9-7E0B-430C-98ED-F13BA22925A1}">
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="62"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="63" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" s="64"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" s="64"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="64"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="64"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="64"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="64"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="63"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="63"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="64"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="64"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="64"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="64"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="64"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="64"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="64"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="64"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="64"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="64"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B20" s="63" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" s="64"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21" s="64"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" s="63"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="63"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="64"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" s="64"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="63"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27" s="63"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B28" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="64"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="64"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="C30" s="64"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="63" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="64"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="63" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="64"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="64"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B34" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="64"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="64"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="63"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B37" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="C37" s="63"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B38" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="64"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B39" s="63" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39" s="64"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B40" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="C40" s="63"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B41" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="C41" s="63"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B42" s="63" t="s">
+        <v>217</v>
+      </c>
+      <c r="C42" s="63"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B43" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" s="64"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B44" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="64"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" s="63" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" s="64"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" s="63" t="s">
+        <v>221</v>
+      </c>
+      <c r="C46" s="64"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B47" s="63" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="64"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B48" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" s="63"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B49" s="63" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" s="64"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B50" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50" s="64"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B51" s="63" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="64"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" s="63" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="64"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B53" s="63" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53" s="64"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B54" s="63" t="s">
+        <v>229</v>
+      </c>
+      <c r="C54" s="64"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B55" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="C55" s="64"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B56" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="C56" s="64"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" s="63" t="s">
+        <v>233</v>
+      </c>
+      <c r="C57" s="64"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B58" s="63" t="s">
+        <v>234</v>
+      </c>
+      <c r="C58" s="64"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="64"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C60" s="64"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="63"/>
+      <c r="C61" s="63"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="63"/>
+      <c r="C62" s="63"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B63" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="C63" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B64" s="63" t="s">
+        <v>238</v>
+      </c>
+      <c r="C64" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B65" s="63" t="s">
+        <v>239</v>
+      </c>
+      <c r="C65" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B66" s="63" t="s">
+        <v>240</v>
+      </c>
+      <c r="C66" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B67" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="C67" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B68" s="63" t="s">
+        <v>242</v>
+      </c>
+      <c r="C68" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B69" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="C69" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B70" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="C70" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B71" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="C71" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A71" xr:uid="{B64128A5-693C-4F8A-960A-6DD37BC38AFA}">
+      <formula1>"營建,機電,消防,文件清冊"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C63" r:id="rId1" xr:uid="{C7F88836-34E5-47AC-AFE1-09540D157E8A}"/>
+    <hyperlink ref="C64" r:id="rId2" xr:uid="{D4861EB4-0A1D-4115-B111-19413BDF6C5C}"/>
+    <hyperlink ref="C65" r:id="rId3" xr:uid="{3DA95DA4-8A31-46E8-AC07-712FFD2F0A9E}"/>
+    <hyperlink ref="C66" r:id="rId4" xr:uid="{CB48EC1D-8C53-43B1-9898-B2D13052F21D}"/>
+    <hyperlink ref="C67" r:id="rId5" xr:uid="{104CF486-B09F-4ED2-A938-37D3E0E3C4B9}"/>
+    <hyperlink ref="C68" r:id="rId6" xr:uid="{C5086B21-2DB1-4920-92C4-F45658ECF408}"/>
+    <hyperlink ref="C69" r:id="rId7" xr:uid="{D6C2FCE3-50E7-42C5-9CF1-C54040DE1BCF}"/>
+    <hyperlink ref="C70" r:id="rId8" xr:uid="{E40043F1-B957-489F-899C-D517F583F941}"/>
+    <hyperlink ref="C71" r:id="rId9" xr:uid="{84534B85-5909-48B4-BBE5-13CF71E3C53F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8BE73D1-DA0F-4543-8B69-3CC8A257CEE8}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2833,46 +3779,46 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="30">
+      <c r="A2" s="51">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="52" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="28"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
       <c r="C3" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
+      <c r="A4" s="51">
         <v>2</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="52" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30"/>
-      <c r="B5" s="28"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30">
+      <c r="A6" s="51">
         <v>3</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="53" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -2880,17 +3826,17 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30"/>
-      <c r="B7" s="36"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="20" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="30">
         <v>4</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="42" t="s">
         <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2898,102 +3844,110 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="32"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="46"/>
       <c r="C9" s="21" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
-        <v>5</v>
-      </c>
-      <c r="B10" s="32"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="46"/>
       <c r="C10" s="19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="33"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30">
-        <v>6</v>
-      </c>
-      <c r="B12" s="30"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="51"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="51"/>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
-        <v>7</v>
-      </c>
-      <c r="B14" s="30"/>
+        <v>6</v>
+      </c>
+      <c r="B14" s="51"/>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
-        <v>8</v>
-      </c>
-      <c r="B16" s="30"/>
+        <v>7</v>
+      </c>
+      <c r="B16" s="51"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="51"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
-        <v>9</v>
-      </c>
-      <c r="B18" s="30"/>
+        <v>8</v>
+      </c>
+      <c r="B18" s="51"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="51"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="30">
-        <v>10</v>
-      </c>
-      <c r="B20" s="30"/>
+        <v>9</v>
+      </c>
+      <c r="B20" s="51"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="51"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="30">
-        <v>11</v>
-      </c>
-      <c r="B22" s="30"/>
+        <v>10</v>
+      </c>
+      <c r="B22" s="51"/>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
+      <c r="A23" s="31"/>
+      <c r="B23" s="51"/>
       <c r="C23" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A8:A11"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A22:A23"/>
@@ -3004,17 +3958,6 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3022,7 +3965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{693BA923-3812-4E67-A320-245B5FD79DF2}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3043,343 +3986,141 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="30">
+      <c r="A2" s="51">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="52" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="28"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
       <c r="C3" s="16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
+      <c r="A4" s="51">
         <v>2</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="28"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30">
+      <c r="A6" s="51">
         <v>3</v>
       </c>
-      <c r="B6" s="28"/>
+      <c r="B6" s="52"/>
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="28"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30">
+      <c r="A8" s="51">
         <v>4</v>
       </c>
-      <c r="B8" s="28"/>
+      <c r="B8" s="52"/>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="28"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
+      <c r="A10" s="51">
         <v>5</v>
       </c>
-      <c r="B10" s="30"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30">
+      <c r="A12" s="51">
         <v>6</v>
       </c>
-      <c r="B12" s="30"/>
+      <c r="B12" s="51"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
+      <c r="A14" s="51">
         <v>7</v>
       </c>
-      <c r="B14" s="30"/>
+      <c r="B14" s="51"/>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30">
+      <c r="A16" s="51">
         <v>8</v>
       </c>
-      <c r="B16" s="30"/>
+      <c r="B16" s="51"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30">
+      <c r="A18" s="51">
         <v>9</v>
       </c>
-      <c r="B18" s="30"/>
+      <c r="B18" s="51"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+      <c r="A20" s="51">
         <v>10</v>
       </c>
-      <c r="B20" s="30"/>
+      <c r="B20" s="51"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="51"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
+      <c r="A22" s="51">
         <v>11</v>
       </c>
-      <c r="B22" s="30"/>
+      <c r="B22" s="51"/>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07458B1E-2302-47BA-BCDE-62F6D02A18BC}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="30">
-        <v>1</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
-        <v>2</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30">
-        <v>3</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30">
-        <v>4</v>
-      </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
-        <v>5</v>
-      </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30">
-        <v>6</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
-        <v>7</v>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30">
-        <v>8</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30">
-        <v>9</v>
-      </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
-        <v>10</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
-        <v>11</v>
-      </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="51"/>
       <c r="C23" s="4"/>
     </row>
   </sheetData>
@@ -3414,948 +4155,182 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3BCF58-CBE3-4280-BAE6-50BE357CA4D2}">
-  <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
-    <col min="3" max="3" width="51.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="30">
-        <v>1</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
-        <v>2</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30">
-        <v>3</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30">
-        <v>3</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
-        <v>4</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
-      <c r="B12" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="41"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
-        <v>5</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30">
-        <v>6</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30">
-        <v>7</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
-        <v>8</v>
-      </c>
-      <c r="B22" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30">
-        <v>9</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <v>10</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>11</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30">
-        <v>12</v>
-      </c>
-      <c r="B28" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="30">
-        <v>13</v>
-      </c>
-      <c r="B30" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E31" t="e" vm="9">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F31" t="e" vm="10">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G31" t="e" vm="11">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="30">
-        <v>14</v>
-      </c>
-      <c r="B32" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D33" t="e" vm="12">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E33" t="e" vm="13">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="44">
-        <v>15</v>
-      </c>
-      <c r="B34" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="44">
-        <v>16</v>
-      </c>
-      <c r="B36" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A37" s="41"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D37" t="e" vm="14">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="30">
-        <v>17</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="30"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="30">
-        <v>18</v>
-      </c>
-      <c r="B40" s="43"/>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="30"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="3"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="30">
-        <v>15</v>
-      </c>
-      <c r="B42" s="30"/>
-      <c r="C42" s="4"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="4"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="30">
-        <v>16</v>
-      </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="4"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="4"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="30">
-        <v>17</v>
-      </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="4"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="4"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="30">
-        <v>18</v>
-      </c>
-      <c r="B48" s="30"/>
-      <c r="C48" s="4"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="30"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="4"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="30">
-        <v>19</v>
-      </c>
-      <c r="B50" s="30"/>
-      <c r="C50" s="4"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="30"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="4"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="30">
-        <v>20</v>
-      </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="4"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="4"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="30">
-        <v>21</v>
-      </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="4"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="4"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="30">
-        <v>22</v>
-      </c>
-      <c r="B56" s="30"/>
-      <c r="C56" s="4"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="4"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="30">
-        <v>23</v>
-      </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="4"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="4"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="30">
-        <v>24</v>
-      </c>
-      <c r="B60" s="30"/>
-      <c r="C60" s="4"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="4"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="30">
-        <v>25</v>
-      </c>
-      <c r="B62" s="30"/>
-      <c r="C62" s="4"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="4"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="30">
-        <v>26</v>
-      </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="4"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="30"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4897B01-73C0-4E75-A8BC-0D435AE77B79}">
-  <dimension ref="A1:D33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07458B1E-2302-47BA-BCDE-62F6D02A18BC}">
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="80.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="37">
+      <c r="A2" s="51">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="8" t="s">
-        <v>70</v>
+      <c r="B2" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="9" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="37">
+      <c r="A4" s="51">
         <v>2</v>
       </c>
-      <c r="B4" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="38"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="23" t="s">
-        <v>68</v>
+      <c r="B4" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37">
+      <c r="A6" s="51">
         <v>3</v>
       </c>
-      <c r="B6" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="23" t="s">
-        <v>61</v>
+      <c r="B6" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="51"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="19" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="37">
+      <c r="A8" s="51">
         <v>4</v>
       </c>
-      <c r="B8" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="38"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="41">
+      <c r="B8" s="52"/>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="51">
         <v>5</v>
       </c>
-      <c r="B10" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="30">
+      <c r="B10" s="51"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="51">
         <v>6</v>
       </c>
-      <c r="B12" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="30"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="22" t="s">
-        <v>62</v>
-      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
+      <c r="A14" s="51">
         <v>7</v>
       </c>
-      <c r="B14" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="30"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="23" t="s">
-        <v>6</v>
-      </c>
+      <c r="B14" s="51"/>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30">
+      <c r="A16" s="51">
         <v>8</v>
       </c>
-      <c r="B16" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30">
+      <c r="B16" s="51"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="51">
         <v>9</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="26" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+      <c r="B18" s="51"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="51">
         <v>10</v>
       </c>
-      <c r="B20" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
+      <c r="B20" s="51"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="51"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="51">
         <v>11</v>
       </c>
-      <c r="B22" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="30">
-        <v>12</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="132" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="18" t="e" vm="15">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="30">
-        <v>13</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" t="e" vm="16">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="30">
-        <v>14</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="26" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="30">
-        <v>15</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="26" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="30">
-        <v>16</v>
-      </c>
-      <c r="B32" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="4" t="s">
-        <v>78</v>
-      </c>
+      <c r="B22" s="51"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="51"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
+  <mergeCells count="22">
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="A16:A17"/>
@@ -4378,13 +4353,12 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47BE74F-DBF9-413C-80FF-83DC058DEDFA}">
-  <dimension ref="A1:D65"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3BCF58-CBE3-4280-BAE6-50BE357CA4D2}">
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34.42578125" customWidth="1"/>
@@ -4403,401 +4377,920 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="30">
+      <c r="A2" s="51">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>83</v>
+      <c r="B2" s="52" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="285" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D3" t="e" vm="17">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="51">
+        <v>2</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
-        <v>2</v>
-      </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="30">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="51">
         <v>3</v>
       </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="C7" s="3"/>
+      <c r="B6" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="51"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="3" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30">
+      <c r="A8" s="51">
         <v>3</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="3"/>
+      <c r="B8" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="3" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
+      <c r="A10" s="51">
         <v>4</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="3"/>
+      <c r="B10" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="3" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="41"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="3"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="31"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
+      <c r="A14" s="51">
         <v>5</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="3"/>
+      <c r="B14" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="51"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="3" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30">
+      <c r="A16" s="51">
         <v>6</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30">
+      <c r="B16" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="51"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="51">
         <v>7</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
+      <c r="B18" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="51"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="30"/>
+      <c r="B20" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="51">
         <v>8</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30">
+      <c r="B22" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="51"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="51">
         <v>9</v>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="51"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>10</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>11</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30">
+      <c r="B27" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="51">
         <v>12</v>
       </c>
-      <c r="B28" s="43"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="30">
+      <c r="B28" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="51"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="51">
         <v>13</v>
       </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="30">
+      <c r="B30" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A31" s="51"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E31" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F31" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G31" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="51">
         <v>14</v>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="44">
+      <c r="B32" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="51"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E33" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="30">
         <v>15</v>
       </c>
-      <c r="B34" s="46"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="44">
+      <c r="B34" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="31"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="30">
         <v>16</v>
       </c>
-      <c r="B36" s="46"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="41"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="30">
+      <c r="B36" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A37" s="31"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="51">
         <v>17</v>
       </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="30"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="3"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="30">
+      <c r="B38" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="51"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="51">
         <v>18</v>
       </c>
-      <c r="B40" s="43"/>
+      <c r="B40" s="56"/>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="30"/>
-      <c r="B41" s="43"/>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="51"/>
+      <c r="B41" s="56"/>
       <c r="C41" s="3"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="30">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="51">
         <v>15</v>
       </c>
-      <c r="B42" s="30"/>
+      <c r="B42" s="51"/>
       <c r="C42" s="4"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="51"/>
+      <c r="B43" s="51"/>
       <c r="C43" s="4"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="30">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="51">
         <v>16</v>
       </c>
-      <c r="B44" s="30"/>
+      <c r="B44" s="51"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="51"/>
+      <c r="B45" s="51"/>
       <c r="C45" s="4"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="30">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="51">
         <v>17</v>
       </c>
-      <c r="B46" s="30"/>
+      <c r="B46" s="51"/>
       <c r="C46" s="4"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="51"/>
+      <c r="B47" s="51"/>
       <c r="C47" s="4"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="30">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="51">
         <v>18</v>
       </c>
-      <c r="B48" s="30"/>
+      <c r="B48" s="51"/>
       <c r="C48" s="4"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="30"/>
-      <c r="B49" s="30"/>
+      <c r="A49" s="51"/>
+      <c r="B49" s="51"/>
       <c r="C49" s="4"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="30">
+      <c r="A50" s="51">
         <v>19</v>
       </c>
-      <c r="B50" s="30"/>
+      <c r="B50" s="51"/>
       <c r="C50" s="4"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="30"/>
-      <c r="B51" s="30"/>
+      <c r="A51" s="51"/>
+      <c r="B51" s="51"/>
       <c r="C51" s="4"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="30">
+      <c r="A52" s="51">
         <v>20</v>
       </c>
-      <c r="B52" s="30"/>
+      <c r="B52" s="51"/>
       <c r="C52" s="4"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
+      <c r="A53" s="51"/>
+      <c r="B53" s="51"/>
       <c r="C53" s="4"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="30">
+      <c r="A54" s="51">
         <v>21</v>
       </c>
-      <c r="B54" s="30"/>
+      <c r="B54" s="51"/>
       <c r="C54" s="4"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="51"/>
+      <c r="B55" s="51"/>
       <c r="C55" s="4"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="30">
+      <c r="A56" s="51">
         <v>22</v>
       </c>
-      <c r="B56" s="30"/>
+      <c r="B56" s="51"/>
       <c r="C56" s="4"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
+      <c r="A57" s="51"/>
+      <c r="B57" s="51"/>
       <c r="C57" s="4"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="30">
+      <c r="A58" s="51">
         <v>23</v>
       </c>
-      <c r="B58" s="30"/>
+      <c r="B58" s="51"/>
       <c r="C58" s="4"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
+      <c r="A59" s="51"/>
+      <c r="B59" s="51"/>
       <c r="C59" s="4"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="30">
+      <c r="A60" s="51">
         <v>24</v>
       </c>
-      <c r="B60" s="30"/>
+      <c r="B60" s="51"/>
       <c r="C60" s="4"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
+      <c r="A61" s="51"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="4"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="30">
+      <c r="A62" s="51">
         <v>25</v>
       </c>
-      <c r="B62" s="30"/>
+      <c r="B62" s="51"/>
       <c r="C62" s="4"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="51"/>
+      <c r="B63" s="51"/>
       <c r="C63" s="4"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="30">
+      <c r="A64" s="51">
         <v>26</v>
       </c>
-      <c r="B64" s="30"/>
+      <c r="B64" s="51"/>
       <c r="C64" s="4"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="30"/>
-      <c r="B65" s="30"/>
+      <c r="A65" s="51"/>
+      <c r="B65" s="51"/>
       <c r="C65" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="62">
     <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4897B01-73C0-4E75-A8BC-0D435AE77B79}">
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="58">
+        <v>1</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="59"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="58">
+        <v>2</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="59"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="58">
+        <v>3</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="59"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="58">
+        <v>4</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="59"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="31">
+        <v>5</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="51"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="51">
+        <v>6</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="51"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="51">
+        <v>7</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="51"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="51">
+        <v>8</v>
+      </c>
+      <c r="B16" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="51"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="51">
+        <v>9</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="51"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="51">
+        <v>10</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="51"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="51">
+        <v>11</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A23" s="51"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="51">
+        <v>12</v>
+      </c>
+      <c r="B24" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="51"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="18" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="51">
+        <v>13</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="51"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="51">
+        <v>14</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="51"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="26" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="51">
+        <v>15</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A31" s="51"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="51">
+        <v>16</v>
+      </c>
+      <c r="B32" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="51"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="A10:A11"/>
@@ -4816,36 +5309,433 @@
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47BE74F-DBF9-413C-80FF-83DC058DEDFA}">
+  <dimension ref="A1:D65"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="122.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="51">
+        <v>1</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="51">
+        <v>2</v>
+      </c>
+      <c r="B4" s="52"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="51">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="51"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="51">
+        <v>3</v>
+      </c>
+      <c r="B8" s="52"/>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="51">
+        <v>4</v>
+      </c>
+      <c r="B10" s="52"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="31"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="51">
+        <v>5</v>
+      </c>
+      <c r="B14" s="56"/>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="51"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="51">
+        <v>6</v>
+      </c>
+      <c r="B16" s="56"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="51"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="51">
+        <v>7</v>
+      </c>
+      <c r="B18" s="56"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="51"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="51">
+        <v>8</v>
+      </c>
+      <c r="B22" s="56"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="51"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="51">
+        <v>9</v>
+      </c>
+      <c r="B24" s="56"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="51"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
+        <v>10</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>11</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="51">
+        <v>12</v>
+      </c>
+      <c r="B28" s="56"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="51"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="51">
+        <v>13</v>
+      </c>
+      <c r="B30" s="56"/>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="51"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="51">
+        <v>14</v>
+      </c>
+      <c r="B32" s="56"/>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="51"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="30">
+        <v>15</v>
+      </c>
+      <c r="B34" s="32"/>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="31"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="30">
+        <v>16</v>
+      </c>
+      <c r="B36" s="32"/>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="31"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="51">
+        <v>17</v>
+      </c>
+      <c r="B38" s="52"/>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="51"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="51">
+        <v>18</v>
+      </c>
+      <c r="B40" s="56"/>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="51"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="51">
+        <v>15</v>
+      </c>
+      <c r="B42" s="51"/>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="51"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="4"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="51">
+        <v>16</v>
+      </c>
+      <c r="B44" s="51"/>
+      <c r="C44" s="4"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="51"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="4"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="51">
+        <v>17</v>
+      </c>
+      <c r="B46" s="51"/>
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="51"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="51">
+        <v>18</v>
+      </c>
+      <c r="B48" s="51"/>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="51"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="51">
+        <v>19</v>
+      </c>
+      <c r="B50" s="51"/>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="51"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="51">
+        <v>20</v>
+      </c>
+      <c r="B52" s="51"/>
+      <c r="C52" s="4"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="51"/>
+      <c r="B53" s="51"/>
+      <c r="C53" s="4"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="51">
+        <v>21</v>
+      </c>
+      <c r="B54" s="51"/>
+      <c r="C54" s="4"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="51"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="4"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="51">
+        <v>22</v>
+      </c>
+      <c r="B56" s="51"/>
+      <c r="C56" s="4"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="51"/>
+      <c r="B57" s="51"/>
+      <c r="C57" s="4"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="51">
+        <v>23</v>
+      </c>
+      <c r="B58" s="51"/>
+      <c r="C58" s="4"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="51"/>
+      <c r="B59" s="51"/>
+      <c r="C59" s="4"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="51">
+        <v>24</v>
+      </c>
+      <c r="B60" s="51"/>
+      <c r="C60" s="4"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="51"/>
+      <c r="B61" s="51"/>
+      <c r="C61" s="4"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="51">
+        <v>25</v>
+      </c>
+      <c r="B62" s="51"/>
+      <c r="C62" s="4"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="51"/>
+      <c r="B63" s="51"/>
+      <c r="C63" s="4"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="51">
+        <v>26</v>
+      </c>
+      <c r="B64" s="51"/>
+      <c r="C64" s="4"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="51"/>
+      <c r="B65" s="51"/>
+      <c r="C65" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="61">
     <mergeCell ref="A64:A65"/>
     <mergeCell ref="B64:B65"/>
     <mergeCell ref="A58:A59"/>
@@ -4854,6 +5744,59 @@
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
